--- a/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
+++ b/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/U34-Bolt/Personal/development/github/trays/non_essential/pocs_prototyping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D7AE31-4F38-B34C-9CE4-EA605C6DAB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03F6854-8BA4-F044-9027-2B4B1F737789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{6B17E38C-5B5E-4043-8C5B-769B1E56F6BE}"/>
   </bookViews>
   <sheets>
     <sheet name="point comparisons" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="use cases" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>for vertical walls</t>
   </si>
@@ -177,20 +177,35 @@
     <t>&gt;</t>
   </si>
   <si>
-    <t>the below image shows each of the use cases above, granted not in the same order… LOL</t>
+    <t>the below image shows each of the use cases above</t>
   </si>
   <si>
     <t>additional info</t>
   </si>
   <si>
     <t>the path line is in black and the wall line is in pink</t>
+  </si>
+  <si>
+    <t>path line</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y1</t>
+  </si>
+  <si>
+    <t>y2</t>
+  </si>
+  <si>
+    <t>wall line</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -198,8 +213,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,8 +241,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -236,20 +295,276 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -262,6 +577,171 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -284,15 +764,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>48846</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>156308</xdr:rowOff>
+      <xdr:colOff>732691</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2487246</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>177899</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2233245</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>109514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -315,8 +795,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="986692" y="7600462"/>
+          <a:off x="732691" y="10404231"/>
           <a:ext cx="7772400" cy="2278283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>517770</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>39076</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2018324</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>92416</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9569D455-A7B5-1DAC-4DCD-77B7B802480D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="517770" y="7483230"/>
+          <a:ext cx="7772400" cy="2720340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -747,215 +1271,502 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2119E86-F6BB-DC4B-94C0-4B0F858BED7B}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="B1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="49" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" style="1" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="6" max="11" width="5.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="59" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="F3" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="60">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="F4" s="25">
+        <v>0</v>
+      </c>
+      <c r="G4" s="55">
+        <v>0</v>
+      </c>
+      <c r="H4" s="56">
+        <v>20</v>
+      </c>
+      <c r="I4" s="25">
+        <v>25</v>
+      </c>
+      <c r="J4" s="55">
+        <v>80</v>
+      </c>
+      <c r="K4" s="56">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B5" s="61">
         <v>2.1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="E5" s="14"/>
+      <c r="F5" s="26">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
+        <v>40</v>
+      </c>
+      <c r="H5" s="28">
+        <v>100</v>
+      </c>
+      <c r="I5" s="52">
+        <v>0</v>
+      </c>
+      <c r="J5" s="53">
+        <v>0</v>
+      </c>
+      <c r="K5" s="54">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="62">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="E6" s="16"/>
+      <c r="F6" s="49">
+        <v>0</v>
+      </c>
+      <c r="G6" s="50">
+        <v>0</v>
+      </c>
+      <c r="H6" s="51">
+        <v>20</v>
+      </c>
+      <c r="I6" s="29">
+        <v>0</v>
+      </c>
+      <c r="J6" s="30">
+        <v>40</v>
+      </c>
+      <c r="K6" s="31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="61">
         <v>3.1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="E7" s="14"/>
+      <c r="F7" s="26">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28">
+        <v>50</v>
+      </c>
+      <c r="I7" s="52">
+        <v>0</v>
+      </c>
+      <c r="J7" s="53">
+        <v>50</v>
+      </c>
+      <c r="K7" s="54">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="62">
         <v>3.2</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="E8" s="16"/>
+      <c r="F8" s="49">
+        <v>0</v>
+      </c>
+      <c r="G8" s="50">
+        <v>50</v>
+      </c>
+      <c r="H8" s="51">
+        <v>100</v>
+      </c>
+      <c r="I8" s="29">
+        <v>0</v>
+      </c>
+      <c r="J8" s="30">
+        <v>0</v>
+      </c>
+      <c r="K8" s="31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B9" s="61">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="E9" s="14"/>
+      <c r="F9" s="26">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
+        <v>25</v>
+      </c>
+      <c r="H9" s="28">
+        <v>100</v>
+      </c>
+      <c r="I9" s="52">
+        <v>0</v>
+      </c>
+      <c r="J9" s="53">
+        <v>0</v>
+      </c>
+      <c r="K9" s="54">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="62">
         <v>4.2</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+      <c r="E10" s="16"/>
+      <c r="F10" s="49">
+        <v>0</v>
+      </c>
+      <c r="G10" s="50">
+        <v>0</v>
+      </c>
+      <c r="H10" s="51">
+        <v>75</v>
+      </c>
+      <c r="I10" s="29">
+        <v>0</v>
+      </c>
+      <c r="J10" s="30">
+        <v>25</v>
+      </c>
+      <c r="K10" s="31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="61">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="E11" s="14"/>
+      <c r="F11" s="26">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
+        <v>0</v>
+      </c>
+      <c r="H11" s="28">
+        <v>50</v>
+      </c>
+      <c r="I11" s="32">
+        <v>0</v>
+      </c>
+      <c r="J11" s="33">
+        <v>0</v>
+      </c>
+      <c r="K11" s="34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B12" s="63">
         <v>5.2</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
+      <c r="E12" s="9"/>
+      <c r="F12" s="41">
+        <v>0</v>
+      </c>
+      <c r="G12" s="42">
+        <v>50</v>
+      </c>
+      <c r="H12" s="43">
+        <v>100</v>
+      </c>
+      <c r="I12" s="35">
+        <v>0</v>
+      </c>
+      <c r="J12" s="36">
+        <v>0</v>
+      </c>
+      <c r="K12" s="37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="62">
         <v>5.3</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="E13" s="16"/>
+      <c r="F13" s="44">
+        <v>0</v>
+      </c>
+      <c r="G13" s="45">
+        <v>25</v>
+      </c>
+      <c r="H13" s="46">
+        <v>75</v>
+      </c>
+      <c r="I13" s="38">
+        <v>0</v>
+      </c>
+      <c r="J13" s="39">
+        <v>0</v>
+      </c>
+      <c r="K13" s="40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B14" s="61">
         <v>6.1</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
+      <c r="E14" s="14"/>
+      <c r="F14" s="32">
+        <v>0</v>
+      </c>
+      <c r="G14" s="33">
+        <v>0</v>
+      </c>
+      <c r="H14" s="34">
+        <v>100</v>
+      </c>
+      <c r="I14" s="26">
+        <v>0</v>
+      </c>
+      <c r="J14" s="27">
+        <v>0</v>
+      </c>
+      <c r="K14" s="28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="63">
         <v>6.2</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="E15" s="9"/>
+      <c r="F15" s="35">
+        <v>0</v>
+      </c>
+      <c r="G15" s="36">
+        <v>0</v>
+      </c>
+      <c r="H15" s="37">
+        <v>100</v>
+      </c>
+      <c r="I15" s="41">
+        <v>0</v>
+      </c>
+      <c r="J15" s="42">
+        <v>50</v>
+      </c>
+      <c r="K15" s="43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="62">
         <v>6.3</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+      <c r="E16" s="16"/>
+      <c r="F16" s="38">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39">
+        <v>0</v>
+      </c>
+      <c r="H16" s="40">
+        <v>100</v>
+      </c>
+      <c r="I16" s="44">
+        <v>0</v>
+      </c>
+      <c r="J16" s="45">
+        <v>25</v>
+      </c>
+      <c r="K16" s="46">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="60">
         <v>7</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="8" t="s">
+      <c r="F17" s="25">
+        <v>0</v>
+      </c>
+      <c r="G17" s="47">
+        <v>0</v>
+      </c>
+      <c r="H17" s="48">
+        <v>100</v>
+      </c>
+      <c r="I17" s="25">
+        <v>0</v>
+      </c>
+      <c r="J17" s="47">
+        <v>0</v>
+      </c>
+      <c r="K17" s="48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C22" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="8" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C23" s="8" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
+++ b/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/U34-Bolt/Personal/development/github/trays/non_essential/pocs_prototyping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03F6854-8BA4-F044-9027-2B4B1F737789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7988E217-0ED6-8E4F-B36E-B55756CD9ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{6B17E38C-5B5E-4043-8C5B-769B1E56F6BE}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="97">
   <si>
     <t>for vertical walls</t>
   </si>
@@ -82,20 +82,9 @@
     <t>use case nbr</t>
   </si>
   <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>the line being compared must have the same orientation (i.e., both lines are horizontal or both lines are vertical)</t>
   </si>
   <si>
-    <t>the invarient coordinates of both lines are not equal equal
-e.g., for 2 vertical lines, wall line x's &lt;&gt; to path line x's</t>
-  </si>
-  <si>
-    <t>the varient coordinates of both lines are equal
-e.g., for 2 vertical lines, p1.y of the wall line is equal to p1.y of the path line and p2.y of the wall line is eqaul to p2.y of the path line</t>
-  </si>
-  <si>
     <t>not collinear</t>
   </si>
   <si>
@@ -199,16 +188,381 @@
   </si>
   <si>
     <t>wall line</t>
+  </si>
+  <si>
+    <t>here are some examples of each use case…</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>at the outset, the wall's line type should be set to None, then if after examining all candidate path lines and if none of the use other use cases are a match, then set the wall type to "interior"</t>
+  </si>
+  <si>
+    <t>all use cases after use case #1, the wall line is collinear with one or more path lins</t>
+  </si>
+  <si>
+    <t>lines labeled as "A" in use case #4 diagram
+-- this would be a "combo" wall</t>
+  </si>
+  <si>
+    <t>lines labeled as "B" in use case #4 diagram
+-- this would be a "combo" wall</t>
+  </si>
+  <si>
+    <t>w.pt1.y &lt; p.pt1.y</t>
+  </si>
+  <si>
+    <t>w.pt1.y &lt; p.pt2.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y &gt; p.pt1.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y &lt; p.pt2.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y &gt; p.pt2.y</t>
+  </si>
+  <si>
+    <t>coulld use cases #5 and #4 be combined - as they both result in "combo" walls
+lines labeled as "B" in use case #5 diagram
+-- this would be a "combo" wall</t>
+  </si>
+  <si>
+    <t>coulld use cases #5 and #4 be combined - as they both result in "combo" walls
+lines labeled as "A" in use case #5 diagram
+-- this would be a "combo" wall</t>
+  </si>
+  <si>
+    <t>coulld use cases #5 and #4 be combined - as they both result in "combo" walls
+lines labeled as "c" in use case #5 diagram
+-- this would be a "combo" wall</t>
+  </si>
+  <si>
+    <t>w.pt1.y == p.pt1.y</t>
+  </si>
+  <si>
+    <t>w.pt1.y &gt; p.pt1.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y == p.pt2.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y &gt; w.pt2.y</t>
+  </si>
+  <si>
+    <t>-- line would be an exterior wall</t>
+  </si>
+  <si>
+    <t>w.pt2.y &lt; p.pt1.y</t>
+  </si>
+  <si>
+    <t>w.pt1.y &gt; p.pt2.y</t>
+  </si>
+  <si>
+    <t>w.pt1.y == p.pt2.y</t>
+  </si>
+  <si>
+    <t>w.pt2.y == p.pt1.y</t>
+  </si>
+  <si>
+    <t>condition 1</t>
+  </si>
+  <si>
+    <t>condition 2</t>
+  </si>
+  <si>
+    <t>condition 3</t>
+  </si>
+  <si>
+    <t>check 2.1</t>
+  </si>
+  <si>
+    <t>check 2.2</t>
+  </si>
+  <si>
+    <t>check 3.1</t>
+  </si>
+  <si>
+    <t>check 3.2</t>
+  </si>
+  <si>
+    <t>check 4.1</t>
+  </si>
+  <si>
+    <t>check 4.2</t>
+  </si>
+  <si>
+    <t>check 5.1</t>
+  </si>
+  <si>
+    <t>check 5.2</t>
+  </si>
+  <si>
+    <t>check 5.3</t>
+  </si>
+  <si>
+    <t>check 6.1</t>
+  </si>
+  <si>
+    <t>check 6.2</t>
+  </si>
+  <si>
+    <t>check 6.3</t>
+  </si>
+  <si>
+    <t>check 7</t>
+  </si>
+  <si>
+    <t>interior</t>
+  </si>
+  <si>
+    <t>combo</t>
+  </si>
+  <si>
+    <t>exterior</t>
+  </si>
+  <si>
+    <t>if not w.is_collinear(p): wall_type = "interior"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">lines labeled as "B" in use case #2 diagram
+same as use case #2.1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>-- could we just test for</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> as w.pt1.y must be less than p.pt1.y if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> is true, as the points are normalized</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">lines labeled as "A" in use case #2 diagram
+not sure if we need to explicitly test for use case #2.1 &amp; #2.2 as if none of the other use cases are true, then we default the wall to "interior"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">-- could we just test for this </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 2</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> as w.pt1.y must be less than p.pt1.y if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 2</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> is true, as the points are normalized</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">same as use case #3.1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">-- could we just test for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> as w.pt1.y must be less than p.pt1.y if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> is true, as the points are normalized</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">again, we probably don't need to explicity test for use case #3.1 and #3.2 -- also note: since we are only testing for wall line to path line overlap, walls meeting this use case conditions would still be considered "interior" walls. But later if there were additional wall defined and we were checking for wall to wall overlap, then we'd want to "join" these 2 walls into 1 single wall I'm thinking ??? but that is a completely different section of logic
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">-- could we just test for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> as w.pt1.y must be less than p.pt1.y if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>condition 1</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> is true, as the points are normalized</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -227,13 +581,56 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -271,8 +668,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -322,6 +737,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -552,10 +978,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -573,177 +1001,245 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -772,7 +1268,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>2233245</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>109514</xdr:rowOff>
+      <xdr:rowOff>109513</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -841,6 +1337,50 @@
         <a:xfrm>
           <a:off x="517770" y="7483230"/>
           <a:ext cx="7772400" cy="2720340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2549768</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>29309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>347783</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>55583</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4572500-64D8-9654-9E63-E04824A5E699}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9651999" y="7414847"/>
+          <a:ext cx="7772400" cy="6386043"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1174,94 +1714,94 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1271,503 +1811,1471 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2119E86-F6BB-DC4B-94C0-4B0F858BED7B}">
-  <dimension ref="B1:K23"/>
+  <dimension ref="B1:AC23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="35" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
     <col min="5" max="5" width="49" customWidth="1"/>
     <col min="6" max="11" width="5.5" style="3" customWidth="1"/>
+    <col min="12" max="14" width="16.33203125" style="61" customWidth="1"/>
+    <col min="15" max="23" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F2" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
       <c r="I2" s="17" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="57" t="s">
+    <row r="3" spans="2:29" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="79" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="81" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="83" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="83" t="s">
+        <v>81</v>
+      </c>
+      <c r="U3" s="83" t="s">
+        <v>82</v>
+      </c>
+      <c r="V3" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="X3" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y3" s="83" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" s="83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="23">
+        <v>1</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="30">
+        <v>25</v>
+      </c>
+      <c r="G4" s="31">
+        <v>80</v>
+      </c>
+      <c r="H4" s="32">
+        <v>100</v>
+      </c>
+      <c r="I4" s="30">
+        <v>0</v>
+      </c>
+      <c r="J4" s="31">
+        <v>0</v>
+      </c>
+      <c r="K4" s="67">
+        <v>20</v>
+      </c>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" ht="117" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="24">
+        <v>2.1</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="36">
+        <v>0</v>
+      </c>
+      <c r="G5" s="37">
+        <v>0</v>
+      </c>
+      <c r="H5" s="38">
+        <v>20</v>
+      </c>
+      <c r="I5" s="33">
+        <v>0</v>
+      </c>
+      <c r="J5" s="34">
+        <v>40</v>
+      </c>
+      <c r="K5" s="68">
+        <v>100</v>
+      </c>
+      <c r="L5" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="76"/>
+      <c r="O5" s="84" t="b">
+        <f>AND(G5&lt;J5,H5&lt;J5)</f>
+        <v>1</v>
+      </c>
+      <c r="P5" s="85" t="b">
+        <f t="shared" ref="P5:P17" si="0">AND(G5&gt;K5,H5&gt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="85" t="b">
+        <f t="shared" ref="Q5:Q17" si="1">AND(G5=K5,H5&gt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="85" t="b">
+        <f t="shared" ref="R5:R17" si="2">AND(H5=J5,G5&lt;J5)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="85" t="b">
+        <f t="shared" ref="S5:S17" si="3">AND(G5&lt;J5,H5&gt;J5,H5&lt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="85" t="b">
+        <f t="shared" ref="T5:T17" si="4">AND(G5&gt;J5,G5&lt;K5,H5&gt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="85" t="b">
+        <f t="shared" ref="U5:U17" si="5">AND(G5=J5,H5&gt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="85" t="b">
+        <f t="shared" ref="V5:V17" si="6">AND(H5=K5,G5&lt;J5)</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="85" t="b">
+        <f t="shared" ref="W5:W17" si="7">AND(G5&lt;J5,H5&gt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="85" t="b">
+        <f t="shared" ref="X5:X17" si="8">AND(G5=J5,H5&lt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="85" t="b">
+        <f t="shared" ref="Y5:Y17" si="9">AND(H5=K5,G5&gt;J5)</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="85" t="b">
+        <f t="shared" ref="Z5:Z17" si="10">AND(G5&gt;J5,H5&lt;K5)</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="85" t="b">
+        <f t="shared" ref="AA5:AA17" si="11">AND(G5=J5,H5=K5)</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC5" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L5&amp;" and "&amp;M5&amp;": wall_type = ""interior"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y &lt; p.pt1.y and w.pt2.y &lt; p.pt1.y: wall_type = "interior</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29" ht="117" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="41">
+        <v>0</v>
+      </c>
+      <c r="G6" s="42">
+        <v>40</v>
+      </c>
+      <c r="H6" s="43">
+        <v>100</v>
+      </c>
+      <c r="I6" s="39">
+        <v>0</v>
+      </c>
+      <c r="J6" s="40">
+        <v>0</v>
+      </c>
+      <c r="K6" s="69">
+        <v>20</v>
+      </c>
+      <c r="L6" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" s="76"/>
+      <c r="O6" s="85" t="b">
+        <f t="shared" ref="O6:O17" si="12">AND(G6&lt;J6,H6&lt;J6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="84" t="b">
+        <f>AND(G6&gt;K6,H6&gt;K6)</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="85" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="85" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="85" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="85" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="85" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V6" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC6" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L6&amp;" and "&amp;M6&amp;": wall_type = ""interior"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y &gt; p.pt2.y and w.pt2.y &gt; p.pt2.y: wall_type = "interior</v>
+      </c>
+    </row>
+    <row r="7" spans="2:29" ht="186" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="24">
+        <v>3.1</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="37">
+        <v>50</v>
+      </c>
+      <c r="H7" s="38">
+        <v>100</v>
+      </c>
+      <c r="I7" s="33">
+        <v>0</v>
+      </c>
+      <c r="J7" s="34">
+        <v>0</v>
+      </c>
+      <c r="K7" s="68">
+        <v>50</v>
+      </c>
+      <c r="L7" s="86" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="76"/>
+      <c r="O7" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="85" t="b">
+        <f t="shared" ref="P7:P17" si="13">AND(G7&gt;K7,H7&gt;K7)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="84" t="b">
+        <f>AND(G7=K7,H7&gt;K7)</f>
+        <v>1</v>
+      </c>
+      <c r="R7" s="85" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="85" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="85" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="85" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V7" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W7" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X7" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC7" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L7&amp;" and "&amp;M7&amp;": wall_type = ""interior"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y == p.pt2.y and w.pt2.y &gt; w.pt2.y: wall_type = "interior</v>
+      </c>
+    </row>
+    <row r="8" spans="2:29" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="25">
+        <v>3.2</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="41">
+        <v>0</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0</v>
+      </c>
+      <c r="H8" s="43">
+        <v>50</v>
+      </c>
+      <c r="I8" s="39">
+        <v>0</v>
+      </c>
+      <c r="J8" s="40">
+        <v>50</v>
+      </c>
+      <c r="K8" s="69">
+        <v>100</v>
+      </c>
+      <c r="L8" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="76"/>
+      <c r="O8" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="85" t="b">
+        <f t="shared" ref="Q8:Q17" si="14">AND(G8=K8,H8&gt;K8)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="84" t="b">
+        <f>AND(H8=J8,G8&lt;J8)</f>
+        <v>1</v>
+      </c>
+      <c r="S8" s="85" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="85" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="85" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC8" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L8&amp;" and "&amp;M8&amp;": wall_type = ""interior"</f>
+        <v>elif w.is_collinear(p) and w.pt2.y == p.pt1.y and w.pt1.y &lt; p.pt1.y: wall_type = "interior</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B9" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="E9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="36">
+        <v>0</v>
+      </c>
+      <c r="G9" s="37">
+        <v>0</v>
+      </c>
+      <c r="H9" s="38">
+        <v>75</v>
+      </c>
+      <c r="I9" s="33">
+        <v>0</v>
+      </c>
+      <c r="J9" s="34">
+        <v>25</v>
+      </c>
+      <c r="K9" s="68">
+        <v>100</v>
+      </c>
+      <c r="L9" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="85" t="b">
+        <f t="shared" ref="R9:R17" si="15">AND(H9=J9,G9&lt;J9)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="84" t="b">
+        <f>AND(G9&lt;J9,H9&gt;J9,H9&lt;K9)</f>
+        <v>1</v>
+      </c>
+      <c r="T9" s="85" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="85" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V9" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W9" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC9" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L9&amp;" and "&amp;M9&amp;" and "&amp;N9&amp;": wall_type = ""combo"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y &lt; p.pt1.y and w.pt2.y &gt; p.pt1.y and w.pt2.y &lt; p.pt2.y: wall_type = "combo</v>
+      </c>
+    </row>
+    <row r="10" spans="2:29" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="41">
+        <v>0</v>
+      </c>
+      <c r="G10" s="42">
+        <v>25</v>
+      </c>
+      <c r="H10" s="43">
+        <v>100</v>
+      </c>
+      <c r="I10" s="39">
+        <v>0</v>
+      </c>
+      <c r="J10" s="40">
+        <v>0</v>
+      </c>
+      <c r="K10" s="69">
+        <v>75</v>
+      </c>
+      <c r="L10" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="85" t="b">
+        <f t="shared" ref="S10:S17" si="16">AND(G10&lt;J10,H10&gt;J10,H10&lt;K10)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="84" t="b">
+        <f>AND(G10&gt;J10,G10&lt;K10,H10&gt;K10)</f>
+        <v>1</v>
+      </c>
+      <c r="U10" s="85" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC10" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L10&amp;" and "&amp;M10&amp;" and "&amp;N10&amp;": wall_type = ""combo"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y &gt; p.pt1.y and w.pt1.y &lt; p.pt2.y and w.pt2.y &gt; p.pt2.y: wall_type = "combo</v>
+      </c>
+    </row>
+    <row r="11" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="B11" s="24">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="44">
+        <v>0</v>
+      </c>
+      <c r="G11" s="45">
+        <v>0</v>
+      </c>
+      <c r="H11" s="46">
+        <v>100</v>
+      </c>
+      <c r="I11" s="33">
+        <v>0</v>
+      </c>
+      <c r="J11" s="34">
+        <v>0</v>
+      </c>
+      <c r="K11" s="68">
         <v>50</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="L11" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="76"/>
+      <c r="O11" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="85" t="b">
+        <f t="shared" ref="T11:T17" si="17">AND(G11&gt;J11,G11&lt;K11,H11&gt;K11)</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="84" t="b">
+        <f>AND(G11=J11,H11&gt;K11)</f>
+        <v>1</v>
+      </c>
+      <c r="V11" s="85" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC11" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L11&amp;" and "&amp;M11&amp;": wall_type = ""combo"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y == p.pt1.y and w.pt2.y &gt; p.pt2.y: wall_type = "combo</v>
+      </c>
+    </row>
+    <row r="12" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="B12" s="26">
+        <v>5.2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="50">
+        <v>0</v>
+      </c>
+      <c r="G12" s="51">
+        <v>0</v>
+      </c>
+      <c r="H12" s="52">
+        <v>100</v>
+      </c>
+      <c r="I12" s="47">
+        <v>0</v>
+      </c>
+      <c r="J12" s="48">
         <v>50</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="60">
+      <c r="K12" s="70">
+        <v>100</v>
+      </c>
+      <c r="L12" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="76"/>
+      <c r="O12" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="85" t="b">
+        <f t="shared" ref="U12:U17" si="18">AND(G12=J12,H12&gt;K12)</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="84" t="b">
+        <f>AND(H12=K12,G12&lt;J12)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
+      <c r="W12" s="85" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA12" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC12" t="str">
+        <f t="shared" ref="AC12:AC13" si="19">"elif w.is_collinear(p) and "&amp;L12&amp;" and "&amp;M12&amp;": wall_type = ""combo"</f>
+        <v>elif w.is_collinear(p) and w.pt2.y == p.pt2.y and w.pt1.y &lt; p.pt1.y: wall_type = "combo</v>
+      </c>
+    </row>
+    <row r="13" spans="2:29" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="25">
+        <v>5.3</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="56">
+        <v>0</v>
+      </c>
+      <c r="G13" s="57">
+        <v>0</v>
+      </c>
+      <c r="H13" s="58">
+        <v>100</v>
+      </c>
+      <c r="I13" s="53">
+        <v>0</v>
+      </c>
+      <c r="J13" s="54">
+        <v>25</v>
+      </c>
+      <c r="K13" s="71">
+        <v>75</v>
+      </c>
+      <c r="L13" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="76" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" s="76"/>
+      <c r="O13" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="85" t="b">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="85" t="b">
+        <f t="shared" ref="V13:V17" si="20">AND(H13=K13,G13&lt;J13)</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="84" t="b">
+        <f>AND(G13&lt;J13,H13&gt;K13)</f>
+        <v>1</v>
+      </c>
+      <c r="X13" s="85" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA13" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13" t="str">
+        <f t="shared" si="19"/>
+        <v>elif w.is_collinear(p) and w.pt1.y &lt; p.pt1.y and w.pt2.y &gt; p.pt2.y: wall_type = "combo</v>
+      </c>
+    </row>
+    <row r="14" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B14" s="24">
+        <v>6.1</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="33">
+        <v>0</v>
+      </c>
+      <c r="G14" s="34">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35">
+        <v>50</v>
+      </c>
+      <c r="I14" s="44">
+        <v>0</v>
+      </c>
+      <c r="J14" s="45">
+        <v>0</v>
+      </c>
+      <c r="K14" s="72">
+        <v>100</v>
+      </c>
+      <c r="L14" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="76"/>
+      <c r="O14" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="85" t="b">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="85" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="85" t="b">
+        <f t="shared" ref="W14:W17" si="21">AND(G14&lt;J14,H14&gt;K14)</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="84" t="b">
+        <f>AND(G14=J14,H14&lt;K14)</f>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="85" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC14" t="str">
+        <f>"elif w.is_collinear(p) and "&amp;L14&amp;" and "&amp;M14&amp;": wall_type = ""exterior"</f>
+        <v>elif w.is_collinear(p) and w.pt1.y == p.pt1.y and w.pt2.y &lt; p.pt2.y: wall_type = "exterior</v>
+      </c>
+    </row>
+    <row r="15" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="26">
+        <v>6.2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="47">
+        <v>0</v>
+      </c>
+      <c r="G15" s="48">
+        <v>50</v>
+      </c>
+      <c r="H15" s="49">
+        <v>100</v>
+      </c>
+      <c r="I15" s="50">
+        <v>0</v>
+      </c>
+      <c r="J15" s="51">
+        <v>0</v>
+      </c>
+      <c r="K15" s="73">
+        <v>100</v>
+      </c>
+      <c r="L15" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="76"/>
+      <c r="O15" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="85" t="b">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="85" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="85" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="85" t="b">
+        <f t="shared" ref="X15:X17" si="22">AND(G15=J15,H15&lt;K15)</f>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="84" t="b">
+        <f>AND(H15=K15,G15&gt;J15)</f>
+        <v>1</v>
+      </c>
+      <c r="Z15" s="85" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC15" t="str">
+        <f t="shared" ref="AC15:AC17" si="23">"elif w.is_collinear(p) and "&amp;L15&amp;" and "&amp;M15&amp;": wall_type = ""exterior"</f>
+        <v>elif w.is_collinear(p) and w.pt2.y == p.pt2.y and w.pt1.y &gt; p.pt1.y: wall_type = "exterior</v>
+      </c>
+    </row>
+    <row r="16" spans="2:29" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="25">
+        <v>6.3</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0</v>
+      </c>
+      <c r="G16" s="54">
+        <v>25</v>
+      </c>
+      <c r="H16" s="55">
+        <v>75</v>
+      </c>
+      <c r="I16" s="56">
+        <v>0</v>
+      </c>
+      <c r="J16" s="57">
+        <v>0</v>
+      </c>
+      <c r="K16" s="74">
+        <v>100</v>
+      </c>
+      <c r="L16" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="76"/>
+      <c r="O16" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="85" t="b">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="85" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="85" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="85" t="b">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="85" t="b">
+        <f t="shared" ref="Y16:Y17" si="24">AND(H16=K16,G16&gt;J16)</f>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="84" t="b">
+        <f>AND(G16&gt;J16,H16&lt;K16)</f>
+        <v>1</v>
+      </c>
+      <c r="AA16" s="85" t="b">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC16" t="str">
+        <f t="shared" si="23"/>
+        <v>elif w.is_collinear(p) and w.pt1.y &gt; p.pt1.y and w.pt2.y &lt; p.pt2.y: wall_type = "exterior</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="23">
+        <v>7</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="25">
-        <v>0</v>
-      </c>
-      <c r="G4" s="55">
-        <v>0</v>
-      </c>
-      <c r="H4" s="56">
-        <v>20</v>
-      </c>
-      <c r="I4" s="25">
-        <v>25</v>
-      </c>
-      <c r="J4" s="55">
-        <v>80</v>
-      </c>
-      <c r="K4" s="56">
+      <c r="D17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0</v>
+      </c>
+      <c r="G17" s="59">
+        <v>0</v>
+      </c>
+      <c r="H17" s="60">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B5" s="61">
-        <v>2.1</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="26">
-        <v>0</v>
-      </c>
-      <c r="G5" s="27">
-        <v>40</v>
-      </c>
-      <c r="H5" s="28">
+      <c r="I17" s="30">
+        <v>0</v>
+      </c>
+      <c r="J17" s="59">
+        <v>0</v>
+      </c>
+      <c r="K17" s="75">
         <v>100</v>
       </c>
-      <c r="I5" s="52">
-        <v>0</v>
-      </c>
-      <c r="J5" s="53">
-        <v>0</v>
-      </c>
-      <c r="K5" s="54">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="62">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="49">
-        <v>0</v>
-      </c>
-      <c r="G6" s="50">
-        <v>0</v>
-      </c>
-      <c r="H6" s="51">
-        <v>20</v>
-      </c>
-      <c r="I6" s="29">
-        <v>0</v>
-      </c>
-      <c r="J6" s="30">
-        <v>40</v>
-      </c>
-      <c r="K6" s="31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B7" s="61">
-        <v>3.1</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="26">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0</v>
-      </c>
-      <c r="H7" s="28">
+      <c r="L17" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="76"/>
+      <c r="O17" s="85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="85" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="85" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="85" t="b">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="85" t="b">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="85" t="b">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="85" t="b">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="85" t="b">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="85" t="b">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="85" t="b">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="85" t="b">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="85" t="b">
+        <f t="shared" ref="Z17" si="25">AND(G17&gt;J17,H17&lt;K17)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="84" t="b">
+        <f>AND(G17=J17,H17=K17)</f>
+        <v>1</v>
+      </c>
+      <c r="AB17" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC17" t="str">
+        <f t="shared" si="23"/>
+        <v>elif w.is_collinear(p) and w.pt1.y == p.pt1.y and w.pt2.y == p.pt2.y: wall_type = "exterior</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="I21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="52">
-        <v>0</v>
-      </c>
-      <c r="J7" s="53">
-        <v>50</v>
-      </c>
-      <c r="K7" s="54">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="62">
-        <v>3.2</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="49">
-        <v>0</v>
-      </c>
-      <c r="G8" s="50">
-        <v>50</v>
-      </c>
-      <c r="H8" s="51">
-        <v>100</v>
-      </c>
-      <c r="I8" s="29">
-        <v>0</v>
-      </c>
-      <c r="J8" s="30">
-        <v>0</v>
-      </c>
-      <c r="K8" s="31">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B9" s="61">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="26">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27">
-        <v>25</v>
-      </c>
-      <c r="H9" s="28">
-        <v>100</v>
-      </c>
-      <c r="I9" s="52">
-        <v>0</v>
-      </c>
-      <c r="J9" s="53">
-        <v>0</v>
-      </c>
-      <c r="K9" s="54">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="62">
-        <v>4.2</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="49">
-        <v>0</v>
-      </c>
-      <c r="G10" s="50">
-        <v>0</v>
-      </c>
-      <c r="H10" s="51">
-        <v>75</v>
-      </c>
-      <c r="I10" s="29">
-        <v>0</v>
-      </c>
-      <c r="J10" s="30">
-        <v>25</v>
-      </c>
-      <c r="K10" s="31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="61">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="26">
-        <v>0</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
-      </c>
-      <c r="H11" s="28">
-        <v>50</v>
-      </c>
-      <c r="I11" s="32">
-        <v>0</v>
-      </c>
-      <c r="J11" s="33">
-        <v>0</v>
-      </c>
-      <c r="K11" s="34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="63">
-        <v>5.2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="41">
-        <v>0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>50</v>
-      </c>
-      <c r="H12" s="43">
-        <v>100</v>
-      </c>
-      <c r="I12" s="35">
-        <v>0</v>
-      </c>
-      <c r="J12" s="36">
-        <v>0</v>
-      </c>
-      <c r="K12" s="37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="62">
-        <v>5.3</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="44">
-        <v>0</v>
-      </c>
-      <c r="G13" s="45">
-        <v>25</v>
-      </c>
-      <c r="H13" s="46">
-        <v>75</v>
-      </c>
-      <c r="I13" s="38">
-        <v>0</v>
-      </c>
-      <c r="J13" s="39">
-        <v>0</v>
-      </c>
-      <c r="K13" s="40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="61">
-        <v>6.1</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="32">
-        <v>0</v>
-      </c>
-      <c r="G14" s="33">
-        <v>0</v>
-      </c>
-      <c r="H14" s="34">
-        <v>100</v>
-      </c>
-      <c r="I14" s="26">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27">
-        <v>0</v>
-      </c>
-      <c r="K14" s="28">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B15" s="63">
-        <v>6.2</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="35">
-        <v>0</v>
-      </c>
-      <c r="G15" s="36">
-        <v>0</v>
-      </c>
-      <c r="H15" s="37">
-        <v>100</v>
-      </c>
-      <c r="I15" s="41">
-        <v>0</v>
-      </c>
-      <c r="J15" s="42">
-        <v>50</v>
-      </c>
-      <c r="K15" s="43">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="62">
-        <v>6.3</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="38">
-        <v>0</v>
-      </c>
-      <c r="G16" s="39">
-        <v>0</v>
-      </c>
-      <c r="H16" s="40">
-        <v>100</v>
-      </c>
-      <c r="I16" s="44">
-        <v>0</v>
-      </c>
-      <c r="J16" s="45">
-        <v>25</v>
-      </c>
-      <c r="K16" s="46">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="69" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="60">
-        <v>7</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="25">
-        <v>0</v>
-      </c>
-      <c r="G17" s="47">
-        <v>0</v>
-      </c>
-      <c r="H17" s="48">
-        <v>100</v>
-      </c>
-      <c r="I17" s="25">
-        <v>0</v>
-      </c>
-      <c r="J17" s="47">
-        <v>0</v>
-      </c>
-      <c r="K17" s="48">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C22" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C23" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="I2:K2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
+++ b/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/U34-Bolt/Personal/development/github/trays/non_essential/pocs_prototyping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7988E217-0ED6-8E4F-B36E-B55756CD9ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F3D609-403B-6646-805B-84095DAC8B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{6B17E38C-5B5E-4043-8C5B-769B1E56F6BE}"/>
   </bookViews>
   <sheets>
     <sheet name="point comparisons" sheetId="3" r:id="rId1"/>
     <sheet name="use cases" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="corner types logic" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,46 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="97">
-  <si>
-    <t>for vertical walls</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>probably interior to the tray's overall base</t>
-  </si>
-  <si>
-    <t>continue</t>
-  </si>
-  <si>
-    <t>from this col to the right only comparying Y coordinates of the wall and path line</t>
-  </si>
-  <si>
-    <t>wall X == path X</t>
-  </si>
-  <si>
-    <t>wall p1 &gt;= path p1</t>
-  </si>
-  <si>
-    <t>wall p2 &lt;= path p2</t>
-  </si>
-  <si>
-    <t>exterior wall</t>
-  </si>
-  <si>
-    <t>wall p1 &lt; path p2</t>
-  </si>
-  <si>
-    <t>combo wall</t>
-  </si>
-  <si>
-    <t>???</t>
-  </si>
-  <si>
-    <t>wall p2 &gt; path p1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>use case nbr</t>
   </si>
@@ -1714,94 +1675,94 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1826,102 +1787,102 @@
   <sheetData>
     <row r="1" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="27" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="16"/>
       <c r="I2" s="17" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="19"/>
     </row>
     <row r="3" spans="2:29" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F3" s="78" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G3" s="79" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H3" s="80" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I3" s="78" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J3" s="79" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K3" s="81" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="L3" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q3" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="U3" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="V3" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y3" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="M3" s="82" t="s">
+      <c r="Z3" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="82" t="s">
+      <c r="AA3" s="83" t="s">
         <v>75</v>
-      </c>
-      <c r="O3" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="P3" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q3" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="R3" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="S3" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="T3" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="U3" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="V3" s="83" t="s">
-        <v>83</v>
-      </c>
-      <c r="W3" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="X3" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y3" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z3" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA3" s="83" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:29" ht="69" thickBot="1" x14ac:dyDescent="0.25">
@@ -1929,11 +1890,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="11" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F4" s="30">
         <v>25</v>
@@ -1970,10 +1931,10 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="2:29" ht="117" customHeight="1" x14ac:dyDescent="0.2">
@@ -1981,13 +1942,13 @@
         <v>2.1</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F5" s="36">
         <v>0</v>
@@ -2008,10 +1969,10 @@
         <v>100</v>
       </c>
       <c r="L5" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="77" t="s">
         <v>56</v>
-      </c>
-      <c r="M5" s="77" t="s">
-        <v>69</v>
       </c>
       <c r="N5" s="76"/>
       <c r="O5" s="84" t="b">
@@ -2067,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="AB5" s="87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L5&amp;" and "&amp;M5&amp;": wall_type = ""interior"</f>
@@ -2079,13 +2040,13 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F6" s="41">
         <v>0</v>
@@ -2106,10 +2067,10 @@
         <v>20</v>
       </c>
       <c r="L6" s="86" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M6" s="76" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="N6" s="76"/>
       <c r="O6" s="85" t="b">
@@ -2165,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AC6" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L6&amp;" and "&amp;M6&amp;": wall_type = ""interior"</f>
@@ -2177,13 +2138,13 @@
         <v>3.1</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F7" s="36">
         <v>0</v>
@@ -2204,10 +2165,10 @@
         <v>50</v>
       </c>
       <c r="L7" s="86" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="M7" s="76" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="N7" s="76"/>
       <c r="O7" s="85" t="b">
@@ -2263,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AC7" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L7&amp;" and "&amp;M7&amp;": wall_type = ""interior"</f>
@@ -2275,13 +2236,13 @@
         <v>3.2</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F8" s="41">
         <v>0</v>
@@ -2302,10 +2263,10 @@
         <v>100</v>
       </c>
       <c r="L8" s="86" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M8" s="76" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="N8" s="76"/>
       <c r="O8" s="85" t="b">
@@ -2361,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AC8" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L8&amp;" and "&amp;M8&amp;": wall_type = ""interior"</f>
@@ -2373,13 +2334,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F9" s="36">
         <v>0</v>
@@ -2400,13 +2361,13 @@
         <v>100</v>
       </c>
       <c r="L9" s="76" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="M9" s="76" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="N9" s="76" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="O9" s="85" t="b">
         <f t="shared" si="12"/>
@@ -2461,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="88" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L9&amp;" and "&amp;M9&amp;" and "&amp;N9&amp;": wall_type = ""combo"</f>
@@ -2473,13 +2434,13 @@
         <v>4.2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F10" s="41">
         <v>0</v>
@@ -2500,13 +2461,13 @@
         <v>75</v>
       </c>
       <c r="L10" s="76" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M10" s="76" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="N10" s="76" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="O10" s="85" t="b">
         <f t="shared" si="12"/>
@@ -2561,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="88" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AC10" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L10&amp;" and "&amp;M10&amp;" and "&amp;N10&amp;": wall_type = ""combo"</f>
@@ -2573,13 +2534,13 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F11" s="44">
         <v>0</v>
@@ -2600,10 +2561,10 @@
         <v>50</v>
       </c>
       <c r="L11" s="76" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M11" s="76" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="N11" s="76"/>
       <c r="O11" s="85" t="b">
@@ -2659,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="88" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L11&amp;" and "&amp;M11&amp;": wall_type = ""combo"</f>
@@ -2671,13 +2632,13 @@
         <v>5.2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="F12" s="50">
         <v>0</v>
@@ -2698,10 +2659,10 @@
         <v>100</v>
       </c>
       <c r="L12" s="76" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="M12" s="76" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="N12" s="76"/>
       <c r="O12" s="85" t="b">
@@ -2757,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="88" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AC12" t="str">
         <f t="shared" ref="AC12:AC13" si="19">"elif w.is_collinear(p) and "&amp;L12&amp;" and "&amp;M12&amp;": wall_type = ""combo"</f>
@@ -2769,13 +2730,13 @@
         <v>5.3</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F13" s="56">
         <v>0</v>
@@ -2796,10 +2757,10 @@
         <v>75</v>
       </c>
       <c r="L13" s="76" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="M13" s="76" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="N13" s="76"/>
       <c r="O13" s="85" t="b">
@@ -2855,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="88" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="str">
         <f t="shared" si="19"/>
@@ -2867,13 +2828,13 @@
         <v>6.1</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F14" s="33">
         <v>0</v>
@@ -2894,10 +2855,10 @@
         <v>100</v>
       </c>
       <c r="L14" s="76" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M14" s="76" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="N14" s="76"/>
       <c r="O14" s="85" t="b">
@@ -2953,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="AB14" s="89" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AC14" t="str">
         <f>"elif w.is_collinear(p) and "&amp;L14&amp;" and "&amp;M14&amp;": wall_type = ""exterior"</f>
@@ -2965,13 +2926,13 @@
         <v>6.2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F15" s="47">
         <v>0</v>
@@ -2992,10 +2953,10 @@
         <v>100</v>
       </c>
       <c r="L15" s="76" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="M15" s="76" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="N15" s="76"/>
       <c r="O15" s="85" t="b">
@@ -3051,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="89" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AC15" t="str">
         <f t="shared" ref="AC15:AC17" si="23">"elif w.is_collinear(p) and "&amp;L15&amp;" and "&amp;M15&amp;": wall_type = ""exterior"</f>
@@ -3063,13 +3024,13 @@
         <v>6.3</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E16" s="64" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F16" s="53">
         <v>0</v>
@@ -3090,10 +3051,10 @@
         <v>100</v>
       </c>
       <c r="L16" s="76" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M16" s="76" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="N16" s="76"/>
       <c r="O16" s="85" t="b">
@@ -3149,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="AB16" s="89" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="str">
         <f t="shared" si="23"/>
@@ -3161,13 +3122,13 @@
         <v>7</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>29</v>
-      </c>
       <c r="E17" s="65" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F17" s="30">
         <v>0</v>
@@ -3188,10 +3149,10 @@
         <v>100</v>
       </c>
       <c r="L17" s="76" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M17" s="76" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="N17" s="76"/>
       <c r="O17" s="85" t="b">
@@ -3247,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="89" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AC17" t="str">
         <f t="shared" si="23"/>
@@ -3256,17 +3217,17 @@
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.2">
       <c r="I21" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C22" s="8" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C23" s="8" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3281,103 +3242,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B50095D-7238-A540-98DB-3313B1FFD71A}">
-  <dimension ref="A1:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6427A672-32E0-C14D-BC40-413C74741AA8}">
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B9" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
+++ b/non_essential/pocs_prototyping/wall line overlapping with path line use cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/U34-Bolt/Personal/development/github/trays/non_essential/pocs_prototyping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F3D609-403B-6646-805B-84095DAC8B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274BD69D-1938-E249-8A9E-98656EEBA63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{6B17E38C-5B5E-4043-8C5B-769B1E56F6BE}"/>
   </bookViews>
